--- a/results/Int Task Remove ACC 0.3/Rando_3_permute.xlsx
+++ b/results/Int Task Remove ACC 0.3/Rando_3_permute.xlsx
@@ -440,557 +440,557 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8598328090071725</v>
+        <v>0.8745705225250203</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8623596567645951</v>
+        <v>0.8736146840731399</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8614038183127147</v>
+        <v>0.8919426008573008</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.861087962343037</v>
+        <v>0.893821195589674</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.816696414365224</v>
+        <v>0.888542620076467</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.844650455352459</v>
+        <v>0.8819096447132326</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8426907305331113</v>
+        <v>0.8510105028017448</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8445693252654844</v>
+        <v>0.8501373697783337</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.875242011837116</v>
+        <v>0.8504532257480115</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9197710083603373</v>
+        <v>0.7394526948579279</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9204109908425399</v>
+        <v>0.7463353618480646</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.8904858038101209</v>
+        <v>0.7463353618480646</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.8955312287821193</v>
+        <v>0.747582244641082</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.8923230458282594</v>
+        <v>0.7557944998527055</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8977008678556294</v>
+        <v>0.7585544981513368</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8976925973127825</v>
+        <v>0.7499172945715307</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9097116652462338</v>
+        <v>0.7533420869809053</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.8766610006884242</v>
+        <v>0.7791694169503595</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8719810549431853</v>
+        <v>0.7816797236220883</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.8885890926505593</v>
+        <v>0.7816797236220883</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.8879656512540506</v>
+        <v>0.7710315966243583</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.8815823675177186</v>
+        <v>0.7710315966243583</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7649062750577756</v>
+        <v>0.7822783533900561</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7655297164542844</v>
+        <v>0.7872576140192791</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7591842409138241</v>
+        <v>0.7972492174491126</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7582284024619437</v>
+        <v>0.8130849439887331</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.8008622631670981</v>
+        <v>0.8654126685812318</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.7851108173974413</v>
+        <v>0.8311233917732517</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.7695232071432285</v>
+        <v>0.8361522756595561</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.786380936477505</v>
+        <v>0.8361522756595561</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.7562556810752651</v>
+        <v>0.8483135181628998</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.8311084260290524</v>
+        <v>0.858222416164264</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.8258810491144217</v>
+        <v>0.8128352523618307</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.8109432672267531</v>
+        <v>0.8078642622754548</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.6940419009330747</v>
+        <v>0.8078642622754548</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.702510542972953</v>
+        <v>0.8202503847771601</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.7012553896370886</v>
+        <v>0.8174076810500597</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6945976026453134</v>
+        <v>0.8099511959204957</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.6346097800350671</v>
+        <v>0.6941151543125761</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.624568553348152</v>
+        <v>0.7003495682776634</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.624983655831993</v>
+        <v>0.7003495682776634</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.6557421985150831</v>
+        <v>0.7066005233284445</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.6557421985150831</v>
+        <v>0.7757198129124441</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.6792132114439107</v>
+        <v>0.7869417580496012</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.6792132114439107</v>
+        <v>0.7822700828472092</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.6465823753944261</v>
+        <v>0.7591613984621517</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.6301877964595775</v>
+        <v>0.7620289138177929</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.615461504167566</v>
+        <v>0.6954447425340629</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.6238407455776226</v>
+        <v>0.6998088323096239</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.6401593142853542</v>
+        <v>0.7423781040134976</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.6344408246597656</v>
+        <v>0.7345395985714803</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.644440698632446</v>
+        <v>0.7339161571749716</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.6864727788866432</v>
+        <v>0.7211826718736954</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.6877279322225076</v>
+        <v>0.6920380665518768</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.7607867570492594</v>
+        <v>0.6783554380000725</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.7482419188919678</v>
+        <v>0.71007808967789</v>
       </c>
     </row>
     <row r="58">
@@ -1000,327 +1000,327 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5584148441278358</v>
+        <v>0.6100431170967087</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.5593624120368693</v>
+        <v>0.7009084206728914</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.5593624120368693</v>
+        <v>0.7294063483111551</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.5583585256694019</v>
+        <v>0.6495641030084296</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5583585256694019</v>
+        <v>0.6476606966475158</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.5583585256694019</v>
+        <v>0.612296643104809</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.5932216206168093</v>
+        <v>0.6090388368938677</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.5718493563942324</v>
+        <v>0.6090388368938677</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5508823487711549</v>
+        <v>0.5885991748361251</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5491128464372864</v>
+        <v>0.5288118144310733</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.5466025397655577</v>
+        <v>0.5058023765601789</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5732963075570707</v>
+        <v>0.4952731878452952</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.5751764776309385</v>
+        <v>0.4939699865938438</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5770137196490769</v>
+        <v>0.4977173301742485</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5554709247097039</v>
+        <v>0.5287720370583333</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.556168800991835</v>
+        <v>0.5157128499030378</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5720986541857611</v>
+        <v>0.4879407608584351</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.5487119220268973</v>
+        <v>0.4899501089348643</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.5167844759547751</v>
+        <v>0.4764443124658347</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5063214515826668</v>
+        <v>0.4847991360827243</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5078991560895614</v>
+        <v>0.4828791886361166</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5145073198242549</v>
+        <v>0.4839011914307724</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5269265244973479</v>
+        <v>0.4735787662870619</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5446077635979539</v>
+        <v>0.4717234078417349</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5446077635979539</v>
+        <v>0.4679827594626825</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5153292542490898</v>
+        <v>0.4679827594626825</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5178230198351248</v>
+        <v>0.499584897516159</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5178230198351248</v>
+        <v>0.499584897516159</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5173996468084369</v>
+        <v>0.4960360469640806</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5167494246065192</v>
+        <v>0.5046468635738512</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5203065457014444</v>
+        <v>0.4960195058783868</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5043400658177677</v>
+        <v>0.495404335024725</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5043400658177677</v>
+        <v>0.4999834589143061</v>
       </c>
     </row>
   </sheetData>
